--- a/reports/historical_reports_EMNonLinTest.xlsx
+++ b/reports/historical_reports_EMNonLinTest.xlsx
@@ -8,6 +8,21 @@
   </bookViews>
   <sheets>
     <sheet name="20260714-214346" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260715-110300" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="20260715-121335" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="20260715-122705" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="20260715-123256" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="20260715-124628" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="20260715-131059" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="20260715-142701" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="20260715-182714" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="20260716-145610" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="20260716-150103" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="20260716-152114" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="20260716-152942" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="20260716-160603" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="20260716-162148" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="20260716-170419" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -883,4 +898,7362 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-09T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-93.594872</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.070719</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.070719</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.464649</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.474163</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.049193</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.277569</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.09433900000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.15035</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.470361</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.538316</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.038381</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.007207</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-5.745718</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>247.582109</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>58.63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.054933</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.054933</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.455287</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.464725</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.022815</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.246959</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.127203</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.140675</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.390492</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.496035</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.055553</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.007186</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-5.91036</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>253.26477</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4834</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>58.67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.09775499999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.09775499999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.278998</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.277267</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.257231</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.126226</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.37432</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.465521</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.209991</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.012107</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.044892</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.004072</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-7.156069</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>402.684938</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>59.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>param.max_hold</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>param.long_only</t>
+        </is>
+      </c>
+      <c r="B21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.026662</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.026662</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.242522</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.241267</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.018828</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.13245</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.102682</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.111849</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.238378</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.015327</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.041978</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-0.003474</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>-10.09948</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>732.5840920000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>57.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>param.max_hold</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>param.long_only</t>
+        </is>
+      </c>
+      <c r="B21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.003162</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.003162</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.213513</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.21131</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.161248</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.26081</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.140334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.024163</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.130866</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.06550300000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.9737130000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-0.002977</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4.331221</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>211.861045</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>57.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>param.max_hold</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>param.long_only</t>
+        </is>
+      </c>
+      <c r="B21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.133645</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.133645</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.926316</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.955724</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.26073</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.211075</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.383931</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.208465</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.641092</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.128193</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.999157</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-0.013336</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>-2.370022</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>74.333001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>56.49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.064014</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>24.416025</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.194938</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.192518</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>16.445344</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>16.502934</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15.716629</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1106.823512</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.02206</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.839266</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.040512</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.000565</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.433181</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>21.857657</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5884</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>57.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.049664</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>11.520448</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.25867</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.254883</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9.6815</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9.687169000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>11.160866</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>479.18435</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.024042</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.641329</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.048062</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.000597</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.839011</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>29.834749</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6569</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>57.06</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0525</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>13.412149</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.214034</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.212055</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12.321816</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>12.307217</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>11.859373</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>427.325886</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.031386</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.800841</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.009746</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.000604</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.915219</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>27.895222</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>56.89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.051151</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12.479921</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.258834</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.25496</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9.962763000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9.973829</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>11.664004</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>530.887502</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.023508</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.6290289999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.061707</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.000592</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.683596</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>26.742362</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6549</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>56.76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.058224</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>18.122117</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.198014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.195969</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14.743494</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>14.760403</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>13.250978</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>820.436821</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.022088</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.8588249999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.06243</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.000581</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-1.118898</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>37.409696</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.249068</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>13.966864</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.32952</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.32662</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.217657000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8.105957999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9.677198000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>161.381846</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.086545</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.835917</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.005115</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.000647</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.456614</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>79.34646100000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>30395</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>17170</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>13225</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>56.49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-16T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:27:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.415432</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.886659</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.626156</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.626723</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-3.253603</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-3.567166</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-4.001702</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-1.572035</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.56402</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.803138</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.978239</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.001198</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.352649</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>376.265506</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>87513</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>46777</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>40736</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>53.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EMNonLinTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.d0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.d_max</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.em_window</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.em_interval</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.em_iters</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.pred_max_dev</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.dead</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.126378</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.126378</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.229838</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.229791</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.371379</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.264319</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6.197738</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5240.163239</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.240634</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.51529</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.052041</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.00308</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-2.606072</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>170.766091</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>60.78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>